--- a/util/gpu_power_bench/docs/flop_unit_worksheet.xlsx
+++ b/util/gpu_power_bench/docs/flop_unit_worksheet.xlsx
@@ -46,11 +46,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -107,15 +107,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -505,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -530,183 +531,267 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>용어</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>정의 / 공식</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>FLOP / FLOPs / FLOPS — 단위 구분 (자주 혼동)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>n_elements</t>
+          <t>표기</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>워크로드의 *output* element 수</t>
+          <t>의미</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>J/element 의 분모</t>
+          <t>종류</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>total_FLOPs</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>n_elements × FLOP_per_elem</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>J/FLOP 의 분모</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>FLOP</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>단일 floating-point 연산 (1 회)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>count, 단수</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>FLOP_per_elem</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>알고리즘이 결정 (sheet 2 참조)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>op 가 정해지면 고정값. matmul 만 K 의존</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>FLOPs</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>여러 FLOP 의 복수형 (개수)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>count, 복수</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>E_total (J)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>NVML power 적분 (그 cell 의 wall_s 동안)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>측정 raw, idle 포함</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>FLOPS</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>FLOPs per second — 처리율 (rate)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>rate, 항상 "초당"</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>E_dyn (J)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>E_total − P_static × wall_s</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>워크로드가 추가로 만든 에너지</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>J/element_dyn</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>E_dyn / n_elements</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>한 element 처리에 든 dyn 에너지</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>에너지는 항상 pJ/FLOP (한 연산 당). pJ/FLOPS 는 단위 분석상 의미 없음.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>J/FLOP_dyn</t>
+          <t>용어</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>E_dyn / total_FLOPs</t>
+          <t>정의 / 공식</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>한 FLOP 에 든 dyn 에너지</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>pJ scale</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>J × 1e12</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>plot bar 위에 표기되는 숫자</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>n_elements</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>워크로드의 *output* element 수</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>J/element 의 분모</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>total_FLOPs</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>n_elements × FLOP_per_elem</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>J/FLOP 의 분모</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>FLOP_per_elem</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>알고리즘이 결정 (sheet 2 참조)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>op 가 정해지면 고정값. matmul 만 K 의존</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>E_total (J)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NVML power 적분 (그 cell 의 wall_s 동안)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>측정 raw, idle 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>E_dyn (J)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>E_total − P_static × wall_s</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>워크로드가 추가로 만든 에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>J/element_dyn</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>E_dyn / n_elements</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한 element 처리에 든 dyn 에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>J/FLOP_dyn</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>E_dyn / total_FLOPs</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한 FLOP 에 든 dyn 에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>pJ scale</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>J × 1e12</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>plot bar 위에 표기되는 숫자</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>변환 공식</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>pJ/FLOP = pJ/elem ÷ FLOP_per_elem</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>pJ/elem = pJ/FLOP × FLOP_per_elem</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -741,107 +826,107 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>op</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>FLOP_per_elem</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>mul, add</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>a±b 한 번</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>softmax</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>max, sub, exp, sum, div (cast 미포함)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>gelu</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>tanh-approx: x, x³, mul, add, tanh, add, mul, mul</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>layernorm</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>mean, var, sub, div, mul, add, ...</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>matmul (M=N=K)</t>
         </is>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <f> 2K</f>
         <v/>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>output 1 개 = K 회의 mul-add. K=4096 → 8192. K=12288 → 24576.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>핵심 — 'FLOP_per_elem 이 5 로 고정' 의 의미</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>softmax 알고리즘이 한 element 를 출력하기 위해 정확히 5 개의 FP 연산을 실행한다. N=128 element row 든 N=1M element row 든 element 1 개 = 5 FLOP. 알고리즘에 박힌 상수 → 입력 크기 N 과 무관.</t>
         </is>
@@ -888,147 +973,147 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>n_elements (= K²)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>total_FLOPs (= 2K³)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>FLOP/elem (= 2K)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>1024</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>A5^2</f>
         <v/>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <f>2*A5^3</f>
         <v/>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <f>2*A5</f>
         <v/>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>2048</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <f>A6^2</f>
         <v/>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <f>2*A6^3</f>
         <v/>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <f>2*A6</f>
         <v/>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>4096</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <f>A7^2</f>
         <v/>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <f>2*A7^3</f>
         <v/>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <f>2*A7</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>← 본 worksheet 의 worked example K</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>8192</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <f>A8^2</f>
         <v/>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <f>2*A8^3</f>
         <v/>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <f>2*A8</f>
         <v/>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="5" t="n">
         <v>12288</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <f>A9^2</f>
         <v/>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <f>2*A9^3</f>
         <v/>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <f>2*A9</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>← 본 sweep 의 최대 default K</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>16384</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <f>A10^2</f>
         <v/>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <f>2*A10^3</f>
         <v/>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <f>2*A10</f>
         <v/>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>← H100 fp8 only sweep 시 권장</t>
         </is>
@@ -1072,215 +1157,215 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>formula / 의미</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>K (= M = N)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="10" t="n">
         <v>4096</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>--matmul-sizes 의 한 값</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>n_elements (= K²)</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <f>B5^2</f>
         <v/>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <f> K^2</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>FLOP per call (= 2K³)</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <f>2*B5^3</f>
         <v/>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <f> 2*K^3</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>FLOP_per_elem (= 2K)</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>2*B5</f>
         <v/>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <f> 2*K (sheet 2)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>iters (3s window 안 호출 수)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>측정 시점 자동 결정 (예시 값)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>total_elements</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>B6*B9</f>
         <v/>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <f> n_elements * iters</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>total_FLOPs</t>
         </is>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <f> FLOP_per_call * iters</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>measured dyn_energy_j</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>21.27</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>측정값 (예시)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>J/element_dyn</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <f>B12/B10</f>
         <v/>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <f> dyn_energy / total_elements</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>J/FLOP_dyn</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>B12/B11</f>
         <v/>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <f> dyn_energy / total_FLOPs</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>pJ/elem (× 1e12)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>B13*1E12</f>
         <v/>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>plot bar 위 표기</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>pJ/FLOP (× 1e12)</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B14*1E12</f>
         <v/>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>← 사용자 실측 0.619 와 일치</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>검증: pJ/FLOP × FLOP/elem</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <f>B16*B8</f>
         <v/>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <f> pJ/elem 과 같아야 함</f>
         <v/>
       </c>
@@ -1331,186 +1416,186 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="10" t="n">
         <v>4096</v>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>n_elements (= K²)</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <f>B5^2</f>
         <v/>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>FLOP per call (= 2K³)</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <f>2*B5^3</f>
         <v/>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>FLOP_per_elem (= 2K)</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>2*B5</f>
         <v/>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>iters (fp8 가 더 빨라 더 많은 iter)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>800</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>total_elements</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>B6*B9</f>
         <v/>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>total_FLOPs</t>
         </is>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <f>B7*B9</f>
         <v/>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>measured dyn_energy_j</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>44.1</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>측정값 (예시)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>J/element_dyn</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <f>B12/B10</f>
         <v/>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>J/FLOP_dyn</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <f>B12/B11</f>
         <v/>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>pJ/elem</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>B13*1E12</f>
         <v/>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>pJ/FLOP</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B14*1E12</f>
         <v/>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>← 사용자 실측 0.401 와 일치</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>검증: pJ/FLOP × FLOP/elem</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <f>B16*B8</f>
         <v/>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <f> pJ/elem</f>
         <v/>
       </c>
@@ -1555,276 +1640,276 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>l2_hit_100 (low N)</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>l2_hit_0 (high N)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>formula / 의미</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>shape</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>(M, D=1024)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>마지막 dim 따라 reduction</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>FLOP_per_elem</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>max, sub, exp, sum, div</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>N (이 cell 의 입력 크기, elements)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="9" t="n">
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>1048576</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>양쪽 다 N=1M elements (동일 size, 다른 cache regime)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>FLOP per call (= 5N)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="10">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="11">
         <f>5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <f>5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>iters (예시; cache regime 별로 다를 수 있음)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>total_elements</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="10">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="11">
         <f>C7*C9</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <f>D7*D9</f>
         <v/>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>total_FLOPs</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="10">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="11">
         <f>C8*C9</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <f>D8*D9</f>
         <v/>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>measured dyn_energy_j</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="15" t="n">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="16" t="n">
         <v>16.27</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>62.13</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>측정값 (l2_hit_100 &lt; l2_hit_0 — DRAM 트래픽 차이)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>J/element_dyn</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="12">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="13">
         <f>C12/C10</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>D12/D10</f>
         <v/>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>J/FLOP_dyn</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="12">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="13">
         <f>C12/C11</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>D12/D11</f>
         <v/>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>pJ/elem</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="13">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="14">
         <f>C13*1E12</f>
         <v/>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="14">
         <f>D13*1E12</f>
         <v/>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>← 사용자 실측 1940 / 7407 과 일치</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>pJ/FLOP</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="16">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="17">
         <f>C14*1E12</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <f>D14*1E12</f>
         <v/>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <f> pJ/elem ÷ 5</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>검증: pJ/FLOP × FLOP_per_elem</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="13">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="14">
         <f>C16*B6</f>
         <v/>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="14">
         <f>D16*B6</f>
         <v/>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <f> pJ/elem (위와 같아야)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>왜 softmax fp8 의 pJ/elem 이 작은 N (l2_hit_100, ~1940) 과 큰 N (l2_hit_0, ~7407) 에서 4× 차이가 나는가:</t>
         </is>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>FLOP_per_elem (=5) 은 동일. 하지만 fp8 softmax 는 cast-compute-cast 패턴 :  (1) fp8 → fp16 cast — 새 fp16 텐서 materialize  (2) fp16 으로 softmax 실행 — 입력 read + 출력 write  (3) fp16 → fp8 cast — 또 다른 read + write  → element 1 개당 ~10 byte DRAM 라운드트립. l2_hit_0 에선 매번 DRAM 까지 → +5500 pJ/elem 추가. l2_hit_100 에선 cache 에 fit → cast/compute 의 *순수 비용* 만 (~1940 pJ/elem).</t>
         </is>
@@ -1872,201 +1957,201 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>matmul bf16 K=4096</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>matmul fp8 K=4096</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>softmax fp8 (l2_hit_100)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>softmax fp8 (l2_hit_0)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>FLOP_per_elem</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>8192</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>8192</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>n_elements (output)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>16,777,216</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>16,777,216</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>1,048,576</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1,048,576</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>pJ/elem (실측 환산)</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>5072</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>3286</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>1940</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>7407</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>pJ/FLOP (실측 환산)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>0.619</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0.401</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <f>1940/5</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <f>7407/5</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>matmul fp8 대비 pJ/elem 배수</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="20">
         <f>B7/C7</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <f>C7/C7</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>E7/C7</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>matmul fp8 대비 pJ/FLOP 배수</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>B8/C8</f>
         <v/>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>C8/C8</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>D8/C8</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>E8/C8</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>관찰</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>1) pJ/FLOP 단위 (행 8) — softmax fp8 가 matmul fp8 보다 ~1000× 비싸 보임.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   하지만 그건 softmax 의 FLOP 카운트가 5 (작음) 인데 cast / DRAM round-trip 같은 *non-FLOP* 비용이 같이 측정되기 때문.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>2) pJ/elem 단위 (행 7) — 같은 자릿수. element 1 개 처리하는 *절대 비용* 이 비슷.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">   l2_hit_100 의 softmax (1940) 는 matmul fp8 (3286) 보다 *싸다*. matmul 이 K=4096 → 8192 FLOP/elem 으로 무겁기 때문.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>3) **결론** — 단위 차이만 풀면 측정은 일관됨. matmul 은 K-비교가 의미 있어 pJ/FLOP, elementwise 는 N 무관해 pJ/elem 이 자연 단위.</t>
         </is>
@@ -2107,72 +2192,72 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>질문</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>답</t>
         </is>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>FLOP_per_elem 이 5 로 고정 이라는 게 무슨 뜻?</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>softmax 알고리즘이 한 element 를 출력하기 위해 정확히 5 개의 FP 연산 (max, sub, exp, sum, div) 을 실행. N=128 든 N=1M 이든 element 1 개 = 5 FLOP. 알고리즘에 박힌 상수 → 입력 크기 N 과 무관.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>matmul 은 왜 변동?</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>matmul output element 1 개를 만들려면 K 번의 곱·덧셈 = 2K FLOP 필요. K=1024 → 2048, K=4096 → 8192, K=12288 → 24576. K 에 비례.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>왜 plot panel 마다 단위 통일 안 함?</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>matmul 은 K 마다 FLOP/elem 이 달라서 pJ/elem 으로 보면 K 가 클수록 자동 커짐 → K 비교 무의미. elementwise 는 FLOP/elem 가 고정이라 pJ/elem 이 자연 단위. 통일하면 한쪽이 무조건 왜곡됨.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>같은 op (softmax) 인데 cache regime 마다 pJ/elem 이 1940→7407 로 바뀌는 이유?</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>FLOP_per_elem 은 5 로 동일. 하지만 *DRAM 트래픽* 은 working set 따라 변함. l2_hit_0 (working set ≫ L2) 에선 cast tensor 들이 매번 DRAM → 추가 ~5500 pJ/elem. l2_hit_100 (cached) 에선 메모리 비용 거의 0 → 1940 pJ/elem 가 cast + compute 의 *순수 비용*.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>matmul fp8 가 bf16 보다 작은 이유?</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>(1) Hopper FP8 Tensor Core 는 native — cast 없음 (matmul fp8_te 의 emulation 은 pre-Hopper 만). (2) FP8 peak throughput 이 fp16/bf16 의 2× → 같은 K 에서 wall_s 가 절반 → static 에너지 절반. 결과: pJ/FLOP 이 ~0.6× 수준.</t>
         </is>
